--- a/RQ 2/mock_trend_analysis.xlsx
+++ b/RQ 2/mock_trend_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stevens0-my.sharepoint.com/personal/gzhao9_stevens_edu/Documents/PHD/2025 Fall/mock pattern/RQ 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{E0CABC7E-C0D3-4F31-B3DA-0F47C6E399DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12A66E8B-7CEF-4858-9D95-BA27242F9553}"/>
+  <xr:revisionPtr revIDLastSave="225" documentId="8_{E0CABC7E-C0D3-4F31-B3DA-0F47C6E399DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCC3990C-F2A2-40C9-AE6B-F3E06437040D}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="3000" windowWidth="30936" windowHeight="16776" xr2:uid="{52D1E1EB-359C-4E11-BAD0-A47CDA1D9EC9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{52D1E1EB-359C-4E11-BAD0-A47CDA1D9EC9}"/>
   </bookViews>
   <sheets>
     <sheet name="mock_trend_analysis" sheetId="1" r:id="rId1"/>
@@ -40,18 +40,12 @@
     <t>Archiva</t>
   </si>
   <si>
-    <t>Aries</t>
-  </si>
-  <si>
     <t>Avro</t>
   </si>
   <si>
     <t>Axiom</t>
   </si>
   <si>
-    <t>Axis2</t>
-  </si>
-  <si>
     <t>Beam</t>
   </si>
   <si>
@@ -133,9 +127,6 @@
     <t>Felix</t>
   </si>
   <si>
-    <t>Fineract</t>
-  </si>
-  <si>
     <t>Flink</t>
   </si>
   <si>
@@ -233,9 +224,6 @@
   </si>
   <si>
     <t>MyFaces</t>
-  </si>
-  <si>
-    <t>NiFi</t>
   </si>
   <si>
     <t>OFBiz</t>
@@ -724,6 +712,22 @@
   </si>
   <si>
     <t>Decreasing</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Axis2</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fineract</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>NiFi</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aries</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1425,7 +1429,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1320" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -1452,11 +1456,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>mock_trend_analysis!$BB$1</c:f>
+              <c:f>mock_trend_analysis!$BT$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Ignite</c:v>
+                  <c:v>NiFi</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1464,7 +1468,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1482,13 +1486,11 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="75000"/>
@@ -1547,8 +1549,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-2.7227034120734909E-2"/>
-                  <c:y val="0.1367507569730988"/>
+                  <c:x val="-0.23737463126843658"/>
+                  <c:y val="0.22155792386031653"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -1564,7 +1566,7 @@
                 <a:lstStyle/>
                 <a:p>
                   <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
                         <a:schemeClr val="tx1">
                           <a:lumMod val="65000"/>
@@ -1583,39 +1585,39 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>mock_trend_analysis!$BB$2:$BB$11</c:f>
+              <c:f>mock_trend_analysis!$BT$2:$BT$11</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>0.89080000000000004</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>0.7873</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.94030000000000002</c:v>
+                  <c:v>0.79179999999999995</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.92130000000000001</c:v>
+                  <c:v>0.7792</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.91180000000000005</c:v>
+                  <c:v>0.7409</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.92859999999999998</c:v>
+                  <c:v>0.72829999999999995</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.89019999999999999</c:v>
+                  <c:v>0.7258</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.90539999999999998</c:v>
+                  <c:v>0.65480000000000005</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.90539999999999998</c:v>
+                  <c:v>0.62229999999999996</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.90669999999999995</c:v>
+                  <c:v>0.61180000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1647,6 +1649,62 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Project Timeline (Year Index)</a:t>
+                </a:r>
+                <a:endParaRPr lang="zh-CN"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="zh-CN"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1668,7 +1726,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1697,53 +1755,12 @@
           <c:max val="1"/>
           <c:min val="0"/>
         </c:scaling>
-        <c:delete val="0"/>
+        <c:delete val="1"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
         <c:numFmt formatCode="0%" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
-          </a:p>
-        </c:txPr>
         <c:crossAx val="995619151"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -1787,7 +1804,7 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr sz="1100"/>
       </a:pPr>
       <a:endParaRPr lang="zh-CN"/>
     </a:p>
@@ -2360,23 +2377,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>143827</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>158114</xdr:rowOff>
+      <xdr:col>74</xdr:col>
+      <xdr:colOff>531754</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>104081</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>181927</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>98107</xdr:rowOff>
+      <xdr:col>81</xdr:col>
+      <xdr:colOff>569854</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>46846</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="图表 1">
+        <xdr:cNvPr id="3" name="图表 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85C6ADA5-89CA-1768-F1DB-B541EAF0CAE8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28EE5460-6567-914D-9654-F3C29BA11E54}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2715,13 +2732,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B644421-D7B0-4157-977E-9C6BAE096056}">
   <dimension ref="A1:DG15"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="10.46484375" customWidth="1"/>
-    <col min="41" max="41" width="7.796875" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" customWidth="1"/>
+    <col min="39" max="39" width="9.5546875" customWidth="1"/>
+    <col min="41" max="41" width="7.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:111" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2741,324 +2759,324 @@
         <v>5</v>
       </c>
       <c r="G1" t="s">
+        <v>232</v>
+      </c>
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
+        <v>229</v>
+      </c>
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="V1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AM1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AN1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AO1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AP1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AQ1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AR1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AS1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AT1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AU1" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AV1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AW1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AX1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AY1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AZ1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BA1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BB1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BC1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BD1" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BE1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BF1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BG1" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BH1" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BI1" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BJ1" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BK1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BL1" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BM1" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BN1" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BO1" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BP1" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BQ1" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BR1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BS1" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BT1" t="s">
+        <v>231</v>
+      </c>
+      <c r="BU1" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BV1" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" t="s">
+      <c r="BW1" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" t="s">
+      <c r="BX1" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" t="s">
+      <c r="BY1" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" t="s">
+      <c r="BZ1" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" t="s">
+      <c r="CA1" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" t="s">
+      <c r="CB1" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" t="s">
+      <c r="CC1" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CD1" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" t="s">
+      <c r="CE1" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CF1" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CG1" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CH1" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CI1" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CJ1" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CK1" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CL1" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CM1" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" t="s">
+      <c r="CN1" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" t="s">
+      <c r="CO1" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CP1" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CQ1" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CR1" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CS1" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" t="s">
+      <c r="CT1" t="s">
         <v>93</v>
       </c>
-      <c r="CQ1" t="s">
+      <c r="CU1" t="s">
         <v>94</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CV1" t="s">
         <v>95</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CW1" t="s">
         <v>96</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CX1" t="s">
         <v>97</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CY1" t="s">
         <v>98</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CZ1" t="s">
         <v>99</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="DA1" t="s">
         <v>100</v>
       </c>
-      <c r="CX1" t="s">
+      <c r="DB1" t="s">
         <v>101</v>
       </c>
-      <c r="CY1" t="s">
+      <c r="DC1" t="s">
         <v>102</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DD1" t="s">
         <v>103</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DE1" t="s">
         <v>104</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DF1" t="s">
         <v>105</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DG1" t="s">
         <v>106</v>
       </c>
-      <c r="DD1" t="s">
+    </row>
+    <row r="2" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="DE1" t="s">
-        <v>108</v>
-      </c>
-      <c r="DF1" t="s">
-        <v>109</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="2" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="B2" s="1">
         <v>0.51519999999999999</v>
@@ -3391,9 +3409,9 @@
         <v>0.81820000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B3" s="1">
         <v>0.51519999999999999</v>
@@ -3726,9 +3744,9 @@
         <v>0.81820000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B4" s="1">
         <v>0.54290000000000005</v>
@@ -4061,9 +4079,9 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="5" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B5" s="1">
         <v>0.55559999999999998</v>
@@ -4369,9 +4387,9 @@
         <v>0.83520000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B6" s="1">
         <v>0.55559999999999998</v>
@@ -4659,9 +4677,9 @@
         <v>0.8387</v>
       </c>
     </row>
-    <row r="7" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B7" s="1">
         <v>0.55559999999999998</v>
@@ -4925,9 +4943,9 @@
         <v>0.86109999999999998</v>
       </c>
     </row>
-    <row r="8" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B8" s="1">
         <v>0.41670000000000001</v>
@@ -5158,9 +5176,9 @@
         <v>0.85580000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B9" s="1">
         <v>0.41670000000000001</v>
@@ -5364,9 +5382,9 @@
         <v>0.86670000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B10" s="1">
         <v>0.41670000000000001</v>
@@ -5543,9 +5561,9 @@
         <v>0.86670000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:111" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B11" s="1">
         <v>0.45100000000000001</v>
@@ -5683,1014 +5701,1014 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="12" spans="1:111" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" t="s">
+        <v>223</v>
+      </c>
+      <c r="E12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G12" t="s">
+        <v>225</v>
+      </c>
+      <c r="H12" t="s">
+        <v>223</v>
+      </c>
+      <c r="I12" t="s">
+        <v>223</v>
+      </c>
+      <c r="J12" t="s">
+        <v>223</v>
+      </c>
+      <c r="K12" t="s">
+        <v>223</v>
+      </c>
+      <c r="L12" t="s">
+        <v>120</v>
+      </c>
+      <c r="M12" t="s">
+        <v>223</v>
+      </c>
+      <c r="N12" t="s">
+        <v>223</v>
+      </c>
+      <c r="O12" t="s">
+        <v>118</v>
+      </c>
+      <c r="P12" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>120</v>
+      </c>
+      <c r="R12" t="s">
+        <v>223</v>
+      </c>
+      <c r="S12" t="s">
+        <v>223</v>
+      </c>
+      <c r="T12" t="s">
+        <v>226</v>
+      </c>
+      <c r="U12" t="s">
+        <v>118</v>
+      </c>
+      <c r="V12" t="s">
+        <v>119</v>
+      </c>
+      <c r="W12" t="s">
+        <v>118</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC12" t="s">
         <v>121</v>
       </c>
-      <c r="B12" t="s">
+      <c r="AD12" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>227</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AM12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>223</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>223</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>223</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>223</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>223</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>228</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>118</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>119</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>119</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>119</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>228</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>119</v>
+      </c>
+      <c r="BN12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BO12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BP12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BQ12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BR12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BS12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BT12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BU12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BV12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BW12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BX12" t="s">
+        <v>118</v>
+      </c>
+      <c r="BY12" t="s">
+        <v>119</v>
+      </c>
+      <c r="BZ12" t="s">
+        <v>119</v>
+      </c>
+      <c r="CA12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>119</v>
+      </c>
+      <c r="CC12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CD12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CE12" t="s">
+        <v>119</v>
+      </c>
+      <c r="CF12" t="s">
+        <v>119</v>
+      </c>
+      <c r="CG12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CI12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CJ12" t="s">
+        <v>121</v>
+      </c>
+      <c r="CK12" t="s">
+        <v>121</v>
+      </c>
+      <c r="CL12" t="s">
+        <v>119</v>
+      </c>
+      <c r="CM12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CN12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CO12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CP12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CQ12" t="s">
+        <v>120</v>
+      </c>
+      <c r="CR12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CS12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CT12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CU12" t="s">
+        <v>121</v>
+      </c>
+      <c r="CV12" t="s">
+        <v>118</v>
+      </c>
+      <c r="CW12" t="s">
+        <v>119</v>
+      </c>
+      <c r="CX12" t="s">
+        <v>120</v>
+      </c>
+      <c r="CY12" t="s">
+        <v>119</v>
+      </c>
+      <c r="CZ12" t="s">
+        <v>119</v>
+      </c>
+      <c r="DA12" t="s">
+        <v>121</v>
+      </c>
+      <c r="DB12" t="s">
+        <v>119</v>
+      </c>
+      <c r="DC12" t="s">
+        <v>118</v>
+      </c>
+      <c r="DD12" t="s">
+        <v>119</v>
+      </c>
+      <c r="DE12" t="s">
+        <v>119</v>
+      </c>
+      <c r="DF12" t="s">
+        <v>118</v>
+      </c>
+      <c r="DG12" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>122</v>
       </c>
-      <c r="C12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D12" t="s">
-        <v>227</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="B13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" t="s">
         <v>124</v>
       </c>
-      <c r="F12" t="s">
-        <v>228</v>
-      </c>
-      <c r="G12" t="s">
-        <v>229</v>
-      </c>
-      <c r="H12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J12" t="s">
-        <v>227</v>
-      </c>
-      <c r="K12" t="s">
-        <v>227</v>
-      </c>
-      <c r="L12" t="s">
+      <c r="F13" t="s">
+        <v>123</v>
+      </c>
+      <c r="G13" t="s">
+        <v>123</v>
+      </c>
+      <c r="H13" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" t="s">
+        <v>125</v>
+      </c>
+      <c r="J13" t="s">
+        <v>125</v>
+      </c>
+      <c r="K13" t="s">
+        <v>123</v>
+      </c>
+      <c r="L13" t="s">
+        <v>123</v>
+      </c>
+      <c r="M13" t="s">
+        <v>125</v>
+      </c>
+      <c r="N13" t="s">
+        <v>123</v>
+      </c>
+      <c r="O13" t="s">
+        <v>123</v>
+      </c>
+      <c r="P13" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>123</v>
+      </c>
+      <c r="R13" t="s">
+        <v>123</v>
+      </c>
+      <c r="S13" t="s">
+        <v>126</v>
+      </c>
+      <c r="T13" t="s">
+        <v>123</v>
+      </c>
+      <c r="U13" t="s">
+        <v>123</v>
+      </c>
+      <c r="V13" t="s">
         <v>124</v>
       </c>
-      <c r="M12" t="s">
-        <v>227</v>
-      </c>
-      <c r="N12" t="s">
-        <v>227</v>
-      </c>
-      <c r="O12" t="s">
-        <v>122</v>
-      </c>
-      <c r="P12" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q12" t="s">
+      <c r="W13" t="s">
+        <v>123</v>
+      </c>
+      <c r="X13" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AG13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ13" t="s">
         <v>124</v>
       </c>
-      <c r="R12" t="s">
-        <v>227</v>
-      </c>
-      <c r="S12" t="s">
-        <v>227</v>
-      </c>
-      <c r="T12" t="s">
-        <v>230</v>
-      </c>
-      <c r="U12" t="s">
-        <v>122</v>
-      </c>
-      <c r="V12" t="s">
-        <v>123</v>
-      </c>
-      <c r="W12" t="s">
-        <v>122</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>123</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>123</v>
-      </c>
-      <c r="AC12" t="s">
+      <c r="AK13" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AQ13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AS13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AV13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AY13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AZ13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BC13" t="s">
         <v>125</v>
       </c>
-      <c r="AD12" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE12" t="s">
+      <c r="BD13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BE13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BF13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BG13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BH13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BI13" t="s">
         <v>125</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="BJ13" t="s">
         <v>125</v>
       </c>
-      <c r="AG12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AH12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AI12" t="s">
-        <v>122</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>231</v>
-      </c>
-      <c r="AK12" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="AL12" t="s">
-        <v>122</v>
-      </c>
-      <c r="AM12" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO12" t="s">
-        <v>227</v>
-      </c>
-      <c r="AP12" t="s">
-        <v>122</v>
-      </c>
-      <c r="AQ12" t="s">
-        <v>227</v>
-      </c>
-      <c r="AR12" t="s">
-        <v>227</v>
-      </c>
-      <c r="AS12" t="s">
-        <v>227</v>
-      </c>
-      <c r="AT12" t="s">
-        <v>227</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>232</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>122</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>122</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>122</v>
-      </c>
-      <c r="AY12" t="s">
-        <v>122</v>
-      </c>
-      <c r="AZ12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BA12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>123</v>
-      </c>
-      <c r="BD12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BE12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BF12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BG12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BH12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BI12" t="s">
-        <v>123</v>
-      </c>
-      <c r="BJ12" t="s">
-        <v>123</v>
-      </c>
-      <c r="BK12" t="s">
-        <v>232</v>
-      </c>
-      <c r="BL12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BM12" t="s">
-        <v>123</v>
-      </c>
-      <c r="BN12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BO12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BP12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BQ12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BR12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BS12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BT12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BU12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BV12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BW12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BX12" t="s">
-        <v>122</v>
-      </c>
-      <c r="BY12" t="s">
-        <v>123</v>
-      </c>
-      <c r="BZ12" t="s">
-        <v>123</v>
-      </c>
-      <c r="CA12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CB12" t="s">
-        <v>123</v>
-      </c>
-      <c r="CC12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CD12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CE12" t="s">
-        <v>123</v>
-      </c>
-      <c r="CF12" t="s">
-        <v>123</v>
-      </c>
-      <c r="CG12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CH12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CI12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CJ12" t="s">
+      <c r="BK13" t="s">
+        <v>124</v>
+      </c>
+      <c r="BL13" t="s">
+        <v>126</v>
+      </c>
+      <c r="BM13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BN13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BO13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BP13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BQ13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BR13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BS13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BT13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BU13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BV13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BW13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BX13" t="s">
+        <v>123</v>
+      </c>
+      <c r="BY13" t="s">
         <v>125</v>
       </c>
-      <c r="CK12" t="s">
+      <c r="BZ13" t="s">
         <v>125</v>
       </c>
-      <c r="CL12" t="s">
-        <v>123</v>
-      </c>
-      <c r="CM12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CN12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CO12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CP12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CQ12" t="s">
-        <v>124</v>
-      </c>
-      <c r="CR12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CS12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CT12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CU12" t="s">
+      <c r="CA13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CB13" t="s">
         <v>125</v>
       </c>
-      <c r="CV12" t="s">
-        <v>122</v>
-      </c>
-      <c r="CW12" t="s">
-        <v>123</v>
-      </c>
-      <c r="CX12" t="s">
-        <v>124</v>
-      </c>
-      <c r="CY12" t="s">
-        <v>123</v>
-      </c>
-      <c r="CZ12" t="s">
-        <v>123</v>
-      </c>
-      <c r="DA12" t="s">
+      <c r="CC13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CD13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CE13" t="s">
         <v>125</v>
       </c>
-      <c r="DB12" t="s">
-        <v>123</v>
-      </c>
-      <c r="DC12" t="s">
-        <v>122</v>
-      </c>
-      <c r="DD12" t="s">
-        <v>123</v>
-      </c>
-      <c r="DE12" t="s">
-        <v>123</v>
-      </c>
-      <c r="DF12" t="s">
-        <v>122</v>
-      </c>
-      <c r="DG12" t="s">
-        <v>122</v>
+      <c r="CF13" t="s">
+        <v>125</v>
+      </c>
+      <c r="CG13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CH13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CI13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CJ13" t="s">
+        <v>127</v>
+      </c>
+      <c r="CK13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CL13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CM13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CN13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CO13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CP13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CQ13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CR13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CS13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CT13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CU13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CV13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CW13" t="s">
+        <v>125</v>
+      </c>
+      <c r="CX13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CY13" t="s">
+        <v>123</v>
+      </c>
+      <c r="CZ13" t="s">
+        <v>125</v>
+      </c>
+      <c r="DA13" t="s">
+        <v>123</v>
+      </c>
+      <c r="DB13" t="s">
+        <v>125</v>
+      </c>
+      <c r="DC13" t="s">
+        <v>123</v>
+      </c>
+      <c r="DD13" t="s">
+        <v>128</v>
+      </c>
+      <c r="DE13" t="s">
+        <v>125</v>
+      </c>
+      <c r="DF13" t="s">
+        <v>123</v>
+      </c>
+      <c r="DG13" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:111" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D13" t="s">
-        <v>127</v>
-      </c>
-      <c r="E13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F13" t="s">
-        <v>127</v>
-      </c>
-      <c r="G13" t="s">
-        <v>127</v>
-      </c>
-      <c r="H13" t="s">
+    <row r="14" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>129</v>
       </c>
-      <c r="I13" t="s">
-        <v>129</v>
-      </c>
-      <c r="J13" t="s">
-        <v>129</v>
-      </c>
-      <c r="K13" t="s">
-        <v>127</v>
-      </c>
-      <c r="L13" t="s">
-        <v>127</v>
-      </c>
-      <c r="M13" t="s">
-        <v>129</v>
-      </c>
-      <c r="N13" t="s">
-        <v>127</v>
-      </c>
-      <c r="O13" t="s">
-        <v>127</v>
-      </c>
-      <c r="P13" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>127</v>
-      </c>
-      <c r="R13" t="s">
-        <v>127</v>
-      </c>
-      <c r="S13" t="s">
+      <c r="B14" t="s">
         <v>130</v>
       </c>
-      <c r="T13" t="s">
-        <v>127</v>
-      </c>
-      <c r="U13" t="s">
-        <v>127</v>
-      </c>
-      <c r="V13" t="s">
-        <v>128</v>
-      </c>
-      <c r="W13" t="s">
-        <v>127</v>
-      </c>
-      <c r="X13" t="s">
+      <c r="C14" t="s">
         <v>131</v>
       </c>
-      <c r="Y13" t="s">
-        <v>129</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>129</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AH13" t="s">
-        <v>129</v>
-      </c>
-      <c r="AI13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>128</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AM13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AO13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AP13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AQ13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AR13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AS13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AW13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>127</v>
-      </c>
-      <c r="AZ13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BA13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BC13" t="s">
-        <v>129</v>
-      </c>
-      <c r="BD13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BE13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BF13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BG13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BH13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BI13" t="s">
-        <v>129</v>
-      </c>
-      <c r="BJ13" t="s">
-        <v>129</v>
-      </c>
-      <c r="BK13" t="s">
-        <v>128</v>
-      </c>
-      <c r="BL13" t="s">
-        <v>130</v>
-      </c>
-      <c r="BM13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BN13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BO13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BP13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BQ13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BR13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BS13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BT13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BU13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BV13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BW13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BX13" t="s">
-        <v>127</v>
-      </c>
-      <c r="BY13" t="s">
-        <v>129</v>
-      </c>
-      <c r="BZ13" t="s">
-        <v>129</v>
-      </c>
-      <c r="CA13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>129</v>
-      </c>
-      <c r="CC13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CD13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CE13" t="s">
-        <v>129</v>
-      </c>
-      <c r="CF13" t="s">
-        <v>129</v>
-      </c>
-      <c r="CG13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CH13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CI13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CJ13" t="s">
-        <v>131</v>
-      </c>
-      <c r="CK13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CL13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CM13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CN13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CO13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CP13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CQ13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CR13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CS13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CT13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CU13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CV13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CW13" t="s">
-        <v>129</v>
-      </c>
-      <c r="CX13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CY13" t="s">
-        <v>127</v>
-      </c>
-      <c r="CZ13" t="s">
-        <v>129</v>
-      </c>
-      <c r="DA13" t="s">
-        <v>127</v>
-      </c>
-      <c r="DB13" t="s">
-        <v>129</v>
-      </c>
-      <c r="DC13" t="s">
-        <v>127</v>
-      </c>
-      <c r="DD13" t="s">
+      <c r="D14" t="s">
         <v>132</v>
       </c>
-      <c r="DE13" t="s">
-        <v>129</v>
-      </c>
-      <c r="DF13" t="s">
-        <v>127</v>
-      </c>
-      <c r="DG13" t="s">
-        <v>127</v>
+      <c r="E14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14" t="s">
+        <v>134</v>
+      </c>
+      <c r="G14" t="s">
+        <v>135</v>
+      </c>
+      <c r="H14" t="s">
+        <v>136</v>
+      </c>
+      <c r="I14" t="s">
+        <v>136</v>
+      </c>
+      <c r="J14" t="s">
+        <v>136</v>
+      </c>
+      <c r="K14" t="s">
+        <v>137</v>
+      </c>
+      <c r="L14" t="s">
+        <v>138</v>
+      </c>
+      <c r="M14" t="s">
+        <v>136</v>
+      </c>
+      <c r="N14" t="s">
+        <v>139</v>
+      </c>
+      <c r="O14" t="s">
+        <v>140</v>
+      </c>
+      <c r="P14" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>142</v>
+      </c>
+      <c r="R14" t="s">
+        <v>143</v>
+      </c>
+      <c r="S14" t="s">
+        <v>144</v>
+      </c>
+      <c r="T14" t="s">
+        <v>145</v>
+      </c>
+      <c r="U14" t="s">
+        <v>146</v>
+      </c>
+      <c r="V14" t="s">
+        <v>147</v>
+      </c>
+      <c r="W14" t="s">
+        <v>148</v>
+      </c>
+      <c r="X14" t="s">
+        <v>149</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>150</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>152</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>153</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>154</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>136</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>155</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>156</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>157</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>158</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>159</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>160</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>161</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>162</v>
+      </c>
+      <c r="AQ14" t="s">
+        <v>163</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>164</v>
+      </c>
+      <c r="AS14" t="s">
+        <v>165</v>
+      </c>
+      <c r="AT14" t="s">
+        <v>166</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>167</v>
+      </c>
+      <c r="AV14" t="s">
+        <v>168</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>169</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>170</v>
+      </c>
+      <c r="AY14" t="s">
+        <v>171</v>
+      </c>
+      <c r="AZ14" t="s">
+        <v>172</v>
+      </c>
+      <c r="BA14" t="s">
+        <v>173</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>174</v>
+      </c>
+      <c r="BC14" t="s">
+        <v>136</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>175</v>
+      </c>
+      <c r="BE14" t="s">
+        <v>176</v>
+      </c>
+      <c r="BF14" t="s">
+        <v>177</v>
+      </c>
+      <c r="BG14" t="s">
+        <v>178</v>
+      </c>
+      <c r="BH14" t="s">
+        <v>179</v>
+      </c>
+      <c r="BI14" t="s">
+        <v>136</v>
+      </c>
+      <c r="BJ14" t="s">
+        <v>136</v>
+      </c>
+      <c r="BK14" t="s">
+        <v>180</v>
+      </c>
+      <c r="BL14" t="s">
+        <v>181</v>
+      </c>
+      <c r="BM14" t="s">
+        <v>182</v>
+      </c>
+      <c r="BN14" t="s">
+        <v>183</v>
+      </c>
+      <c r="BO14" t="s">
+        <v>184</v>
+      </c>
+      <c r="BP14" t="s">
+        <v>185</v>
+      </c>
+      <c r="BQ14" t="s">
+        <v>186</v>
+      </c>
+      <c r="BR14" t="s">
+        <v>187</v>
+      </c>
+      <c r="BS14" t="s">
+        <v>188</v>
+      </c>
+      <c r="BT14" t="s">
+        <v>189</v>
+      </c>
+      <c r="BU14" t="s">
+        <v>190</v>
+      </c>
+      <c r="BV14" t="s">
+        <v>191</v>
+      </c>
+      <c r="BW14" t="s">
+        <v>192</v>
+      </c>
+      <c r="BX14" t="s">
+        <v>193</v>
+      </c>
+      <c r="BY14" t="s">
+        <v>136</v>
+      </c>
+      <c r="BZ14" t="s">
+        <v>136</v>
+      </c>
+      <c r="CA14" t="s">
+        <v>194</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>136</v>
+      </c>
+      <c r="CC14" t="s">
+        <v>195</v>
+      </c>
+      <c r="CD14" t="s">
+        <v>196</v>
+      </c>
+      <c r="CE14" t="s">
+        <v>136</v>
+      </c>
+      <c r="CF14" t="s">
+        <v>136</v>
+      </c>
+      <c r="CG14" t="s">
+        <v>197</v>
+      </c>
+      <c r="CH14" t="s">
+        <v>198</v>
+      </c>
+      <c r="CI14" t="s">
+        <v>199</v>
+      </c>
+      <c r="CJ14" t="s">
+        <v>200</v>
+      </c>
+      <c r="CK14" t="s">
+        <v>201</v>
+      </c>
+      <c r="CL14" t="s">
+        <v>202</v>
+      </c>
+      <c r="CM14" t="s">
+        <v>203</v>
+      </c>
+      <c r="CN14" t="s">
+        <v>204</v>
+      </c>
+      <c r="CO14" t="s">
+        <v>205</v>
+      </c>
+      <c r="CP14" t="s">
+        <v>206</v>
+      </c>
+      <c r="CQ14" t="s">
+        <v>207</v>
+      </c>
+      <c r="CR14" t="s">
+        <v>208</v>
+      </c>
+      <c r="CS14" t="s">
+        <v>209</v>
+      </c>
+      <c r="CT14" t="s">
+        <v>210</v>
+      </c>
+      <c r="CU14" t="s">
+        <v>211</v>
+      </c>
+      <c r="CV14" t="s">
+        <v>212</v>
+      </c>
+      <c r="CW14" t="s">
+        <v>213</v>
+      </c>
+      <c r="CX14" t="s">
+        <v>214</v>
+      </c>
+      <c r="CY14" t="s">
+        <v>215</v>
+      </c>
+      <c r="CZ14" t="s">
+        <v>136</v>
+      </c>
+      <c r="DA14" t="s">
+        <v>216</v>
+      </c>
+      <c r="DB14" t="s">
+        <v>136</v>
+      </c>
+      <c r="DC14" t="s">
+        <v>217</v>
+      </c>
+      <c r="DD14" t="s">
+        <v>218</v>
+      </c>
+      <c r="DE14" t="s">
+        <v>136</v>
+      </c>
+      <c r="DF14" t="s">
+        <v>219</v>
+      </c>
+      <c r="DG14" t="s">
+        <v>220</v>
       </c>
     </row>
-    <row r="14" spans="1:111" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B14" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" t="s">
-        <v>136</v>
-      </c>
-      <c r="E14" t="s">
-        <v>137</v>
-      </c>
-      <c r="F14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G14" t="s">
-        <v>139</v>
-      </c>
-      <c r="H14" t="s">
-        <v>140</v>
-      </c>
-      <c r="I14" t="s">
-        <v>140</v>
-      </c>
-      <c r="J14" t="s">
-        <v>140</v>
-      </c>
-      <c r="K14" t="s">
-        <v>141</v>
-      </c>
-      <c r="L14" t="s">
-        <v>142</v>
-      </c>
-      <c r="M14" t="s">
-        <v>140</v>
-      </c>
-      <c r="N14" t="s">
-        <v>143</v>
-      </c>
-      <c r="O14" t="s">
-        <v>144</v>
-      </c>
-      <c r="P14" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>146</v>
-      </c>
-      <c r="R14" t="s">
-        <v>147</v>
-      </c>
-      <c r="S14" t="s">
-        <v>148</v>
-      </c>
-      <c r="T14" t="s">
-        <v>149</v>
-      </c>
-      <c r="U14" t="s">
-        <v>150</v>
-      </c>
-      <c r="V14" t="s">
-        <v>151</v>
-      </c>
-      <c r="W14" t="s">
-        <v>152</v>
-      </c>
-      <c r="X14" t="s">
-        <v>153</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>140</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>140</v>
-      </c>
-      <c r="AC14" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>140</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>156</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>157</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>158</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>140</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>159</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>160</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>161</v>
-      </c>
-      <c r="AL14" t="s">
-        <v>162</v>
-      </c>
-      <c r="AM14" t="s">
-        <v>163</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>164</v>
-      </c>
-      <c r="AO14" t="s">
-        <v>165</v>
-      </c>
-      <c r="AP14" t="s">
-        <v>166</v>
-      </c>
-      <c r="AQ14" t="s">
-        <v>167</v>
-      </c>
-      <c r="AR14" t="s">
-        <v>168</v>
-      </c>
-      <c r="AS14" t="s">
-        <v>169</v>
-      </c>
-      <c r="AT14" t="s">
-        <v>170</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>171</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>172</v>
-      </c>
-      <c r="AW14" t="s">
-        <v>173</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>174</v>
-      </c>
-      <c r="AY14" t="s">
-        <v>175</v>
-      </c>
-      <c r="AZ14" t="s">
-        <v>176</v>
-      </c>
-      <c r="BA14" t="s">
-        <v>177</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>178</v>
-      </c>
-      <c r="BC14" t="s">
-        <v>140</v>
-      </c>
-      <c r="BD14" t="s">
-        <v>179</v>
-      </c>
-      <c r="BE14" t="s">
-        <v>180</v>
-      </c>
-      <c r="BF14" t="s">
-        <v>181</v>
-      </c>
-      <c r="BG14" t="s">
-        <v>182</v>
-      </c>
-      <c r="BH14" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI14" t="s">
-        <v>140</v>
-      </c>
-      <c r="BJ14" t="s">
-        <v>140</v>
-      </c>
-      <c r="BK14" t="s">
-        <v>184</v>
-      </c>
-      <c r="BL14" t="s">
-        <v>185</v>
-      </c>
-      <c r="BM14" t="s">
-        <v>186</v>
-      </c>
-      <c r="BN14" t="s">
-        <v>187</v>
-      </c>
-      <c r="BO14" t="s">
-        <v>188</v>
-      </c>
-      <c r="BP14" t="s">
-        <v>189</v>
-      </c>
-      <c r="BQ14" t="s">
-        <v>190</v>
-      </c>
-      <c r="BR14" t="s">
-        <v>191</v>
-      </c>
-      <c r="BS14" t="s">
-        <v>192</v>
-      </c>
-      <c r="BT14" t="s">
-        <v>193</v>
-      </c>
-      <c r="BU14" t="s">
-        <v>194</v>
-      </c>
-      <c r="BV14" t="s">
-        <v>195</v>
-      </c>
-      <c r="BW14" t="s">
-        <v>196</v>
-      </c>
-      <c r="BX14" t="s">
-        <v>197</v>
-      </c>
-      <c r="BY14" t="s">
-        <v>140</v>
-      </c>
-      <c r="BZ14" t="s">
-        <v>140</v>
-      </c>
-      <c r="CA14" t="s">
-        <v>198</v>
-      </c>
-      <c r="CB14" t="s">
-        <v>140</v>
-      </c>
-      <c r="CC14" t="s">
-        <v>199</v>
-      </c>
-      <c r="CD14" t="s">
-        <v>200</v>
-      </c>
-      <c r="CE14" t="s">
-        <v>140</v>
-      </c>
-      <c r="CF14" t="s">
-        <v>140</v>
-      </c>
-      <c r="CG14" t="s">
-        <v>201</v>
-      </c>
-      <c r="CH14" t="s">
-        <v>202</v>
-      </c>
-      <c r="CI14" t="s">
-        <v>203</v>
-      </c>
-      <c r="CJ14" t="s">
-        <v>204</v>
-      </c>
-      <c r="CK14" t="s">
-        <v>205</v>
-      </c>
-      <c r="CL14" t="s">
-        <v>206</v>
-      </c>
-      <c r="CM14" t="s">
-        <v>207</v>
-      </c>
-      <c r="CN14" t="s">
-        <v>208</v>
-      </c>
-      <c r="CO14" t="s">
-        <v>209</v>
-      </c>
-      <c r="CP14" t="s">
-        <v>210</v>
-      </c>
-      <c r="CQ14" t="s">
-        <v>211</v>
-      </c>
-      <c r="CR14" t="s">
-        <v>212</v>
-      </c>
-      <c r="CS14" t="s">
-        <v>213</v>
-      </c>
-      <c r="CT14" t="s">
-        <v>214</v>
-      </c>
-      <c r="CU14" t="s">
-        <v>215</v>
-      </c>
-      <c r="CV14" t="s">
-        <v>216</v>
-      </c>
-      <c r="CW14" t="s">
-        <v>217</v>
-      </c>
-      <c r="CX14" t="s">
-        <v>218</v>
-      </c>
-      <c r="CY14" t="s">
-        <v>219</v>
-      </c>
-      <c r="CZ14" t="s">
-        <v>140</v>
-      </c>
-      <c r="DA14" t="s">
-        <v>220</v>
-      </c>
-      <c r="DB14" t="s">
-        <v>140</v>
-      </c>
-      <c r="DC14" t="s">
+    <row r="15" spans="1:111" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>221</v>
-      </c>
-      <c r="DD14" t="s">
-        <v>222</v>
-      </c>
-      <c r="DE14" t="s">
-        <v>140</v>
-      </c>
-      <c r="DF14" t="s">
-        <v>223</v>
-      </c>
-      <c r="DG14" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="15" spans="1:111" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
-        <v>225</v>
       </c>
       <c r="B15">
         <v>0.877</v>
